--- a/reports_excel/VVN品牌主管專用_【主管評下屬用】.xlsx
+++ b/reports_excel/VVN品牌主管專用_【主管評下屬用】.xlsx
@@ -197,9 +197,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -255,6 +252,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -702,19 +702,11 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>部屬自評</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>主管評定</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
           <t>主管評核回饋與觀察</t>
         </is>
       </c>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -732,13 +724,13 @@
           <t>在購買教具、道具或各種印刷時，我會先徵詢同事過往的製作經驗作為參考，並評估當下的需求與預算，在不過度煩死同事的情況下獨立採購合理的品項。</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr"/>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
     </row>
     <row r="6" ht="90" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -758,13 +750,13 @@
 我嘗試在每一個設計階段分享成品、同時向大家詳述畫面中分別運用了哪些需要的元素，最後逐步修整成大家可以接受的設計。</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7" ht="108" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -784,13 +776,13 @@
 因為無法使用針對兒童教材專業的校色印刷，顏色過濾程度不是很理想，因此來回調整試印了很多顏色，並在「謎題可以被解開」的標準下和酷童夥伴確認成品可接受度，也準備了「萬一有家庭無法透過預設操作方式解謎」的備案，完成了這次的教材。</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -808,18 +800,18 @@
           <t>我盡可能不在工作以外的事項上打擾大家(?)</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>二、專業職能：自評 vs 主管評分並列對照【美感設計師】（逐項比對認知差異）</t>
+          <t>二、專業職能：自評 vs 主管評分並列對照【$美感設計師】（逐項比對認知差異）</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -861,7 +853,7 @@
       </c>
     </row>
     <row r="12" ht="108" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>品牌識別系統設計與維護</t>
         </is>
@@ -886,19 +878,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="13" ht="108" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>視覺與美感設計實務</t>
         </is>
@@ -921,19 +913,19 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>需求釐清與創意提案</t>
         </is>
@@ -956,166 +948,171 @@
           <t>尚不公布</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>尚未評分</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>【待主管填寫回饋】</t>
         </is>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>三、評級標準（不對員工公布具體分數與總分，只回饋評級）</t>
         </is>
       </c>
-      <c r="B16" s="10" t="n"/>
-      <c r="C16" s="10" t="n"/>
-      <c r="D16" s="10" t="n"/>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>評級（最終呈現）</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>Level (分數落點）</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>定義</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>回饋方式參考</t>
         </is>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Amazing!</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>L5 (9.0-10.0)</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>遠超職位期待，表現為團隊之標竿與典範。</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>讚賞其突出貢獻，探討經驗複製機制。</t>
         </is>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>L4 (7.0-8.9)</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>優於職位期待，持續展現高標準成果。</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>肯定並具體指出是哪些行為讓它超出標準，並設定具挑戰性的下一步目標。</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>Keep</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="18" t="inlineStr">
         <is>
           <t>L3 (5.0-6.9)</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C20" s="19" t="inlineStr">
         <is>
           <t>符合職位門檻，展現穩定的工作交付。</t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr">
+      <c r="D20" s="19" t="inlineStr">
         <is>
           <t>確認穩定度，維持既有節奏，指出下一階可以再往前的地方，選一到兩項深化</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="21" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>Grow</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>L2 (3.0-4.9)</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>部分符合，部分能力/行為仍在建立階段。</t>
         </is>
       </c>
-      <c r="D21" s="23" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="21" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>L1（1.0-2.9)</t>
         </is>
       </c>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>目前的具體事證還看不到這項職能，或事證與職能要求落差明顯。</t>
         </is>
       </c>
-      <c r="D22" s="23" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="10">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="D7:F7"/>
     <mergeCell ref="A10:F10"/>
+    <mergeCell ref="D5:F5"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D4:F4"/>
     <mergeCell ref="A16:D16"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D6:F6"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="E12 E13 E14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="評分無效" error="請從選單選擇等級：Amazing! (Lv5)、Good (L4)、Keep (L3)、Grow (L2)、Start (Lv1)" promptTitle="等級選單" prompt="請選取評級：Amazing! (Lv5)、Good (L4)、Keep (L3)、Grow (L2)、Start (Lv1)" type="list">
@@ -1160,7 +1157,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>評估對象：林文琇（美感設計師） ｜ 直屬主管：何維安 ｜ 同儕填答樣本：2 位 ｜ 自評狀態：已自評</t>
+          <t>評估對象：林文琇（美感設計師） ｜ 直屬主管：何維安 ｜ 同儕填答樣本：$2 位 ｜ 自評狀態：$已自評</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1221,12 +1218,12 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>Q24</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>合作狀況</t>
         </is>
@@ -1236,28 +1233,28 @@
           <t>合作狀況（溝通順暢度、資訊透明度、承諾事項達成率）</t>
         </is>
       </c>
-      <c r="D5" s="25" t="n">
+      <c r="D5" s="24" t="n">
         <v>9.5</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>10.0, 9.0</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>Q25</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>工作品質</t>
         </is>
@@ -1267,28 +1264,28 @@
           <t>注重細節（工作成果之品質與細緻度）</t>
         </is>
       </c>
-      <c r="D6" s="25" t="n">
+      <c r="D6" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="25" t="inlineStr">
         <is>
           <t>10.0, 8.0</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>Q26</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>專案進度</t>
         </is>
@@ -1298,28 +1295,28 @@
           <t>準時完成（專案進度與時程掌控）</t>
         </is>
       </c>
-      <c r="D7" s="25" t="n">
+      <c r="D7" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>Q27</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>變動彈性</t>
         </is>
@@ -1329,28 +1326,28 @@
           <t>靈活調整（面對臨時變動與突發狀況的彈性）</t>
         </is>
       </c>
-      <c r="D8" s="25" t="n">
+      <c r="D8" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t>10.0, 10.0</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>Q28</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>追蹤承諾</t>
         </is>
@@ -1360,28 +1357,28 @@
           <t>追蹤承諾（主動回報進度與承諾事項追蹤）</t>
         </is>
       </c>
-      <c r="D9" s="25" t="n">
+      <c r="D9" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="25" t="inlineStr">
         <is>
           <t>10.0, 8.0</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>Q29</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>透明溝通</t>
         </is>
@@ -1391,16 +1388,16 @@
           <t>說明決策依據（決策與工作方法透明度）</t>
         </is>
       </c>
-      <c r="D10" s="25" t="n">
+      <c r="D10" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="25" t="inlineStr">
         <is>
           <t>9.0, 7.0</t>
         </is>
@@ -1422,16 +1419,16 @@
           <t>【多元】接受不同意見（能開放聆聽反對觀點）</t>
         </is>
       </c>
-      <c r="D11" s="25" t="n">
+      <c r="D11" s="24" t="n">
         <v>9.5</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="25" t="inlineStr">
         <is>
           <t>10.0, 9.0</t>
         </is>
@@ -1453,16 +1450,16 @@
           <t>【多元】提出建設性觀點（在討論中給予實質建議）</t>
         </is>
       </c>
-      <c r="D12" s="25" t="n">
+      <c r="D12" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="25" t="inlineStr">
         <is>
           <t>9.0, 7.0</t>
         </is>
@@ -1484,16 +1481,16 @@
           <t>【實驗】開放調整（透過回饋持續迭代優化）</t>
         </is>
       </c>
-      <c r="D13" s="25" t="n">
+      <c r="D13" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E13" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F13" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t>10.0, 8.0</t>
         </is>
@@ -1515,16 +1512,16 @@
           <t>【信任】分享經驗與資源（主動協助夥伴）</t>
         </is>
       </c>
-      <c r="D14" s="25" t="n">
+      <c r="D14" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="E14" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="F14" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="25" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
@@ -1546,16 +1543,16 @@
           <t>【可持續】讚美與肯定同儕（經常給予夥伴正向激勵）</t>
         </is>
       </c>
-      <c r="D15" s="25" t="n">
+      <c r="D15" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F15" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="25" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
@@ -1577,28 +1574,28 @@
           <t>【可持續】尊重工作界線（維護彼此身心健康與邊界）</t>
         </is>
       </c>
-      <c r="D16" s="25" t="n">
+      <c r="D16" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E16" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="F16" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="25" t="inlineStr">
         <is>
           <t>10.0</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>Q36</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>NPS推薦</t>
         </is>
@@ -1608,16 +1605,16 @@
           <t>NPS 推薦度（向他人推薦與此夥伴共事的意願）</t>
         </is>
       </c>
-      <c r="D17" s="25" t="n">
+      <c r="D17" s="24" t="n">
         <v>9</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="E17" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="F17" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="25" t="inlineStr">
         <is>
           <t>9.0, 9.0</t>
         </is>
@@ -2024,142 +2021,142 @@
       <c r="G40" s="5" t="n"/>
     </row>
     <row r="42" ht="24" customHeight="1">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>三、評級標準（不對員工公布具體分數與總分，只回饋評級）</t>
         </is>
       </c>
-      <c r="B42" s="10" t="n"/>
-      <c r="C42" s="10" t="n"/>
-      <c r="D42" s="10" t="n"/>
+      <c r="B42" s="9" t="n"/>
+      <c r="C42" s="9" t="n"/>
+      <c r="D42" s="9" t="n"/>
     </row>
     <row r="43" ht="24" customHeight="1">
-      <c r="A43" s="11" t="inlineStr">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>評級（最終呈現）</t>
         </is>
       </c>
-      <c r="B43" s="11" t="inlineStr">
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>Level (分數落點）</t>
         </is>
       </c>
-      <c r="C43" s="11" t="inlineStr">
+      <c r="C43" s="10" t="inlineStr">
         <is>
           <t>定義</t>
         </is>
       </c>
-      <c r="D43" s="11" t="inlineStr">
+      <c r="D43" s="10" t="inlineStr">
         <is>
           <t>回饋方式參考</t>
         </is>
       </c>
     </row>
     <row r="44" ht="28" customHeight="1">
-      <c r="A44" s="12" t="inlineStr">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>Amazing!</t>
         </is>
       </c>
-      <c r="B44" s="13" t="inlineStr">
+      <c r="B44" s="12" t="inlineStr">
         <is>
           <t>L5 (9.0-10.0)</t>
         </is>
       </c>
-      <c r="C44" s="14" t="inlineStr">
+      <c r="C44" s="13" t="inlineStr">
         <is>
           <t>遠超職位期待，表現為團隊之標竿與典範。</t>
         </is>
       </c>
-      <c r="D44" s="14" t="inlineStr">
+      <c r="D44" s="13" t="inlineStr">
         <is>
           <t>讚賞其突出貢獻，探討經驗複製機制。</t>
         </is>
       </c>
     </row>
     <row r="45" ht="28" customHeight="1">
-      <c r="A45" s="15" t="inlineStr">
+      <c r="A45" s="14" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="B45" s="16" t="inlineStr">
+      <c r="B45" s="15" t="inlineStr">
         <is>
           <t>L4 (7.0-8.9)</t>
         </is>
       </c>
-      <c r="C45" s="17" t="inlineStr">
+      <c r="C45" s="16" t="inlineStr">
         <is>
           <t>優於職位期待，持續展現高標準成果。</t>
         </is>
       </c>
-      <c r="D45" s="17" t="inlineStr">
+      <c r="D45" s="16" t="inlineStr">
         <is>
           <t>肯定並具體指出是哪些行為讓它超出標準，並設定具挑戰性的下一步目標。</t>
         </is>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="18" t="inlineStr">
+      <c r="A46" s="17" t="inlineStr">
         <is>
           <t>Keep</t>
         </is>
       </c>
-      <c r="B46" s="19" t="inlineStr">
+      <c r="B46" s="18" t="inlineStr">
         <is>
           <t>L3 (5.0-6.9)</t>
         </is>
       </c>
-      <c r="C46" s="20" t="inlineStr">
+      <c r="C46" s="19" t="inlineStr">
         <is>
           <t>符合職位門檻，展現穩定的工作交付。</t>
         </is>
       </c>
-      <c r="D46" s="20" t="inlineStr">
+      <c r="D46" s="19" t="inlineStr">
         <is>
           <t>確認穩定度，維持既有節奏，指出下一階可以再往前的地方，選一到兩項深化</t>
         </is>
       </c>
     </row>
     <row r="47" ht="28" customHeight="1">
-      <c r="A47" s="21" t="inlineStr">
+      <c r="A47" s="20" t="inlineStr">
         <is>
           <t>Grow</t>
         </is>
       </c>
-      <c r="B47" s="22" t="inlineStr">
+      <c r="B47" s="21" t="inlineStr">
         <is>
           <t>L2 (3.0-4.9)</t>
         </is>
       </c>
-      <c r="C47" s="23" t="inlineStr">
+      <c r="C47" s="22" t="inlineStr">
         <is>
           <t>部分符合，部分能力/行為仍在建立階段。</t>
         </is>
       </c>
-      <c r="D47" s="23" t="inlineStr">
+      <c r="D47" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
       </c>
     </row>
     <row r="48" ht="28" customHeight="1">
-      <c r="A48" s="21" t="inlineStr">
+      <c r="A48" s="20" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="B48" s="22" t="inlineStr">
+      <c r="B48" s="21" t="inlineStr">
         <is>
           <t>L1（1.0-2.9)</t>
         </is>
       </c>
-      <c r="C48" s="23" t="inlineStr">
+      <c r="C48" s="22" t="inlineStr">
         <is>
           <t>目前的具體事證還看不到這項職能，或事證與職能要求落差明顯。</t>
         </is>
       </c>
-      <c r="D48" s="23" t="inlineStr">
+      <c r="D48" s="22" t="inlineStr">
         <is>
           <t>說明落差在哪，聚焦一項具體可練習的行為，納入下一期 IDP，設定可觀察的行為指標</t>
         </is>
